--- a/output/Tables/7000 steps/Resampling/HIA_per_disease_Rubin_7000steps.xlsx
+++ b/output/Tables/7000 steps/Resampling/HIA_per_disease_Rubin_7000steps.xlsx
@@ -480,13 +480,13 @@
         <v>87621.27800000001</v>
       </c>
       <c r="E3">
-        <v>9599.222</v>
+        <v>9600.772999999999</v>
       </c>
       <c r="F3">
-        <v>5637.439</v>
+        <v>5637.121</v>
       </c>
       <c r="G3">
-        <v>13561.006</v>
+        <v>13564.425</v>
       </c>
       <c r="H3">
         <v>3456071941.181</v>
@@ -498,13 +498,13 @@
         <v>4880680442.527</v>
       </c>
       <c r="K3">
-        <v>1276696587.706</v>
+        <v>1276902817.898</v>
       </c>
       <c r="L3">
-        <v>749779429.6440001</v>
+        <v>749737065.197</v>
       </c>
       <c r="M3">
-        <v>1803613745.768</v>
+        <v>1804068570.599</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>10049.596</v>
       </c>
       <c r="E4">
-        <v>1368.521</v>
+        <v>1368.535</v>
       </c>
       <c r="F4">
-        <v>-44.731</v>
+        <v>-44.453</v>
       </c>
       <c r="G4">
-        <v>2781.773</v>
+        <v>2781.523</v>
       </c>
       <c r="H4">
         <v>217972796.284</v>
@@ -541,13 +541,13 @@
         <v>443056534.118</v>
       </c>
       <c r="K4">
-        <v>182013271.916</v>
+        <v>182015170.589</v>
       </c>
       <c r="L4">
-        <v>-5949200.233</v>
+        <v>-5912183.464</v>
       </c>
       <c r="M4">
-        <v>369975744.065</v>
+        <v>369942524.642</v>
       </c>
     </row>
     <row r="5">
@@ -566,13 +566,13 @@
         <v>65823.633</v>
       </c>
       <c r="E5">
-        <v>5526.781</v>
+        <v>5527.045</v>
       </c>
       <c r="F5">
-        <v>-179.002</v>
+        <v>-179.22</v>
       </c>
       <c r="G5">
-        <v>11232.565</v>
+        <v>11233.309</v>
       </c>
       <c r="H5">
         <v>479705689.68</v>
@@ -584,13 +584,13 @@
         <v>974650540.347</v>
       </c>
       <c r="K5">
-        <v>735061934.4859999</v>
+        <v>735096949.5140001</v>
       </c>
       <c r="L5">
-        <v>-23807252.462</v>
+        <v>-23836238.037</v>
       </c>
       <c r="M5">
-        <v>1493931121.434</v>
+        <v>1494030137.065</v>
       </c>
     </row>
     <row r="6">
@@ -609,13 +609,13 @@
         <v>82070.76300000001</v>
       </c>
       <c r="E6">
-        <v>10376.39</v>
+        <v>10377.182</v>
       </c>
       <c r="F6">
-        <v>613.072</v>
+        <v>614.763</v>
       </c>
       <c r="G6">
-        <v>20139.708</v>
+        <v>20139.601</v>
       </c>
       <c r="H6">
         <v>3181459779.404</v>
@@ -627,13 +627,13 @@
         <v>6171803483.887</v>
       </c>
       <c r="K6">
-        <v>1380059888.524</v>
+        <v>1380165206.32</v>
       </c>
       <c r="L6">
-        <v>81538575.024</v>
+        <v>81763511.862</v>
       </c>
       <c r="M6">
-        <v>2678581202.023</v>
+        <v>2678566900.778</v>
       </c>
     </row>
     <row r="7">
@@ -652,13 +652,13 @@
         <v>27049.488</v>
       </c>
       <c r="E7">
-        <v>4298.816</v>
+        <v>4298.894</v>
       </c>
       <c r="F7">
-        <v>2841.247</v>
+        <v>2840.656</v>
       </c>
       <c r="G7">
-        <v>5756.385</v>
+        <v>5757.131</v>
       </c>
       <c r="H7">
         <v>339054012.683</v>
@@ -670,13 +670,13 @@
         <v>455486324.375</v>
       </c>
       <c r="K7">
-        <v>571742528.687</v>
+        <v>571752890.665</v>
       </c>
       <c r="L7">
-        <v>377885912.04</v>
+        <v>377807303.462</v>
       </c>
       <c r="M7">
-        <v>765599145.335</v>
+        <v>765698477.868</v>
       </c>
     </row>
     <row r="8">
@@ -695,13 +695,13 @@
         <v>1625252.524</v>
       </c>
       <c r="E8">
-        <v>1396733.73</v>
+        <v>1396855.288</v>
       </c>
       <c r="F8">
-        <v>920345.89</v>
+        <v>920296.284</v>
       </c>
       <c r="G8">
-        <v>1873121.57</v>
+        <v>1873414.292</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>185765586061.862</v>
+        <v>185781753292.976</v>
       </c>
       <c r="L8">
-        <v>122406003338.658</v>
+        <v>122399405732.96</v>
       </c>
       <c r="M8">
-        <v>249125168785.066</v>
+        <v>249164100852.993</v>
       </c>
     </row>
     <row r="9">
@@ -738,13 +738,13 @@
         <v>1897867.282</v>
       </c>
       <c r="E9">
-        <v>1427903.46</v>
+        <v>1428027.717</v>
       </c>
       <c r="F9">
-        <v>929213.915</v>
+        <v>929165.151</v>
       </c>
       <c r="G9">
-        <v>1926593.007</v>
+        <v>1926890.281</v>
       </c>
       <c r="H9">
         <v>7674264219.231999</v>
@@ -756,13 +756,13 @@
         <v>12925677325.254</v>
       </c>
       <c r="K9">
-        <v>189911160273.181</v>
+        <v>189927686327.962</v>
       </c>
       <c r="L9">
-        <v>123585450802.671</v>
+        <v>123578965191.98</v>
       </c>
       <c r="M9">
-        <v>256236869743.691</v>
+        <v>256276407463.945</v>
       </c>
     </row>
     <row r="10">
@@ -781,13 +781,13 @@
         <v>2119801.384</v>
       </c>
       <c r="E10">
-        <v>1710387.985</v>
+        <v>1710512.242</v>
       </c>
       <c r="F10">
-        <v>1132116.422</v>
+        <v>1132067.658</v>
       </c>
       <c r="G10">
-        <v>2288659.55</v>
+        <v>2288956.824</v>
       </c>
       <c r="H10">
         <v>7674264219.231999</v>
@@ -799,13 +799,13 @@
         <v>12925677325.254</v>
       </c>
       <c r="K10">
-        <v>227481602094.677</v>
+        <v>227498128149.458</v>
       </c>
       <c r="L10">
-        <v>150571484256.403</v>
+        <v>150564998645.712</v>
       </c>
       <c r="M10">
-        <v>304391719932.95</v>
+        <v>304431257653.204</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/Resampling/HIA_per_disease_Rubin_7000steps.xlsx
+++ b/output/Tables/7000 steps/Resampling/HIA_per_disease_Rubin_7000steps.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>172946.361</v>
+        <v>158930.587</v>
       </c>
       <c r="C2">
-        <v>123958.621</v>
+        <v>136322.738</v>
       </c>
       <c r="D2">
-        <v>221934.102</v>
+        <v>181538.436</v>
       </c>
       <c r="E2">
-        <v>282484.525</v>
+        <v>1652101.462</v>
       </c>
       <c r="F2">
-        <v>202902.507</v>
+        <v>1422001.742</v>
       </c>
       <c r="G2">
-        <v>362066.543</v>
+        <v>1882201.183</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>37570441821.496</v>
+        <v>219729494470.641</v>
       </c>
       <c r="L2">
-        <v>26986033453.732</v>
+        <v>189126231623.648</v>
       </c>
       <c r="M2">
-        <v>48154850189.259</v>
+        <v>250332757317.633</v>
       </c>
     </row>
     <row r="3">
@@ -471,341 +471,298 @@
         </is>
       </c>
       <c r="B3">
-        <v>62045.742</v>
+        <v>143213.073</v>
       </c>
       <c r="C3">
-        <v>36470.206</v>
+        <v>95721.712</v>
       </c>
       <c r="D3">
-        <v>87621.27800000001</v>
+        <v>190704.435</v>
       </c>
       <c r="E3">
-        <v>9600.772999999999</v>
+        <v>124950.873</v>
       </c>
       <c r="F3">
-        <v>5637.121</v>
+        <v>83551.893</v>
       </c>
       <c r="G3">
-        <v>13564.425</v>
+        <v>166349.853</v>
       </c>
       <c r="H3">
-        <v>3456071941.181</v>
+        <v>7977254612.368</v>
       </c>
       <c r="I3">
-        <v>2031463439.835</v>
+        <v>5331890774.727</v>
       </c>
       <c r="J3">
-        <v>4880680442.527</v>
+        <v>10622618450.009</v>
       </c>
       <c r="K3">
-        <v>1276902817.898</v>
+        <v>16618466078.747</v>
       </c>
       <c r="L3">
-        <v>749737065.197</v>
+        <v>11112401748.73</v>
       </c>
       <c r="M3">
-        <v>1804068570.599</v>
+        <v>22124530408.764</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B4">
-        <v>4944.151</v>
+        <v>128139.669</v>
       </c>
       <c r="C4">
-        <v>-161.293</v>
+        <v>611.773</v>
       </c>
       <c r="D4">
-        <v>10049.596</v>
+        <v>255667.566</v>
       </c>
       <c r="E4">
-        <v>1368.535</v>
+        <v>189413.998</v>
       </c>
       <c r="F4">
-        <v>-44.453</v>
+        <v>884.752</v>
       </c>
       <c r="G4">
-        <v>2781.523</v>
+        <v>377943.244</v>
       </c>
       <c r="H4">
-        <v>217972796.284</v>
+        <v>1897364083.402</v>
       </c>
       <c r="I4">
-        <v>-7110941.551</v>
+        <v>9058519.049000001</v>
       </c>
       <c r="J4">
-        <v>443056534.118</v>
+        <v>3785669647.755</v>
       </c>
       <c r="K4">
-        <v>182015170.589</v>
+        <v>25192061701.487</v>
       </c>
       <c r="L4">
-        <v>-5912183.464</v>
+        <v>117671991.306</v>
       </c>
       <c r="M4">
-        <v>369942524.642</v>
+        <v>50266451411.668</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B5">
-        <v>32397.224</v>
+        <v>27621.649</v>
       </c>
       <c r="C5">
-        <v>-1029.186</v>
+        <v>2726.917</v>
       </c>
       <c r="D5">
-        <v>65823.633</v>
+        <v>52516.382</v>
       </c>
       <c r="E5">
-        <v>5527.045</v>
+        <v>54245.542</v>
       </c>
       <c r="F5">
-        <v>-179.22</v>
+        <v>5351.667</v>
       </c>
       <c r="G5">
-        <v>11233.309</v>
+        <v>103139.417</v>
       </c>
       <c r="H5">
-        <v>479705689.68</v>
+        <v>2077175638.588</v>
       </c>
       <c r="I5">
-        <v>-15239160.986</v>
+        <v>205066867.493</v>
       </c>
       <c r="J5">
-        <v>974650540.347</v>
+        <v>3949284409.682</v>
       </c>
       <c r="K5">
-        <v>735096949.5140001</v>
+        <v>7214657082.719</v>
       </c>
       <c r="L5">
-        <v>-23836238.037</v>
+        <v>711771743.381</v>
       </c>
       <c r="M5">
-        <v>1494030137.065</v>
+        <v>13717542422.057</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B6">
-        <v>42306.083</v>
+        <v>49286.12</v>
       </c>
       <c r="C6">
-        <v>2541.403</v>
+        <v>37680.747</v>
       </c>
       <c r="D6">
-        <v>82070.76300000001</v>
+        <v>60891.494</v>
       </c>
       <c r="E6">
-        <v>10377.182</v>
+        <v>72555.231</v>
       </c>
       <c r="F6">
-        <v>614.763</v>
+        <v>55583.785</v>
       </c>
       <c r="G6">
-        <v>20139.601</v>
+        <v>89526.678</v>
       </c>
       <c r="H6">
-        <v>3181459779.404</v>
+        <v>829928981.777</v>
       </c>
       <c r="I6">
-        <v>191116074.922</v>
+        <v>634506099.929</v>
       </c>
       <c r="J6">
-        <v>6171803483.887</v>
+        <v>1025351863.626</v>
       </c>
       <c r="K6">
-        <v>1380165206.32</v>
+        <v>9649845786.952999</v>
       </c>
       <c r="L6">
-        <v>81763511.862</v>
+        <v>7392643355.775</v>
       </c>
       <c r="M6">
-        <v>2678566900.778</v>
+        <v>11907048218.131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B7">
-        <v>20135.044</v>
+        <v>614985.331</v>
       </c>
       <c r="C7">
-        <v>13220.601</v>
+        <v>477137.094</v>
       </c>
       <c r="D7">
-        <v>27049.488</v>
+        <v>752833.567</v>
       </c>
       <c r="E7">
-        <v>4298.894</v>
+        <v>1782015.141</v>
       </c>
       <c r="F7">
-        <v>2840.656</v>
+        <v>1381196.8</v>
       </c>
       <c r="G7">
-        <v>5757.131</v>
+        <v>2182833.482</v>
       </c>
       <c r="H7">
-        <v>339054012.683</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>222621700.99</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>455486324.375</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>571752890.665</v>
+        <v>237008013709.751</v>
       </c>
       <c r="L7">
-        <v>377807303.462</v>
+        <v>183699174348.095</v>
       </c>
       <c r="M7">
-        <v>765698477.868</v>
+        <v>290316853071.408</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B8">
-        <v>1214712.073</v>
+        <v>963245.8419999999</v>
       </c>
       <c r="C8">
-        <v>804171.623</v>
+        <v>613878.243</v>
       </c>
       <c r="D8">
-        <v>1625252.524</v>
+        <v>1312613.444</v>
       </c>
       <c r="E8">
-        <v>1396855.288</v>
+        <v>2223180.785</v>
       </c>
       <c r="F8">
-        <v>920296.284</v>
+        <v>1526568.897</v>
       </c>
       <c r="G8">
-        <v>1873414.292</v>
+        <v>2919792.674</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>12781723316.135</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>6180522261.198</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>19382924371.072</v>
       </c>
       <c r="K8">
-        <v>185781753292.976</v>
+        <v>295683044359.657</v>
       </c>
       <c r="L8">
-        <v>122399405732.96</v>
+        <v>203033663187.287</v>
       </c>
       <c r="M8">
-        <v>249164100852.993</v>
+        <v>388332425532.028</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>All</t>
         </is>
       </c>
       <c r="B9">
-        <v>1376540.317</v>
+        <v>1122176.429</v>
       </c>
       <c r="C9">
-        <v>855213.3540000001</v>
+        <v>750200.9809999999</v>
       </c>
       <c r="D9">
-        <v>1897867.282</v>
+        <v>1494151.88</v>
       </c>
       <c r="E9">
-        <v>1428027.717</v>
+        <v>3875282.247</v>
       </c>
       <c r="F9">
-        <v>929165.151</v>
+        <v>2948570.639</v>
       </c>
       <c r="G9">
-        <v>1926890.281</v>
+        <v>4801993.856999999</v>
       </c>
       <c r="H9">
-        <v>7674264219.231999</v>
+        <v>12781723316.135</v>
       </c>
       <c r="I9">
-        <v>2422851113.21</v>
+        <v>6180522261.198</v>
       </c>
       <c r="J9">
-        <v>12925677325.254</v>
+        <v>19382924371.072</v>
       </c>
       <c r="K9">
-        <v>189927686327.962</v>
+        <v>515412538830.298</v>
       </c>
       <c r="L9">
-        <v>123578965191.98</v>
+        <v>392159894810.9351</v>
       </c>
       <c r="M9">
-        <v>256276407463.945</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>1549486.678</v>
-      </c>
-      <c r="C10">
-        <v>979171.975</v>
-      </c>
-      <c r="D10">
-        <v>2119801.384</v>
-      </c>
-      <c r="E10">
-        <v>1710512.242</v>
-      </c>
-      <c r="F10">
-        <v>1132067.658</v>
-      </c>
-      <c r="G10">
-        <v>2288956.824</v>
-      </c>
-      <c r="H10">
-        <v>7674264219.231999</v>
-      </c>
-      <c r="I10">
-        <v>2422851113.21</v>
-      </c>
-      <c r="J10">
-        <v>12925677325.254</v>
-      </c>
-      <c r="K10">
-        <v>227498128149.458</v>
-      </c>
-      <c r="L10">
-        <v>150564998645.712</v>
-      </c>
-      <c r="M10">
-        <v>304431257653.204</v>
+        <v>638665182849.661</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/Resampling/HIA_per_disease_Rubin_7000steps.xlsx
+++ b/output/Tables/7000 steps/Resampling/HIA_per_disease_Rubin_7000steps.xlsx
@@ -372,7 +372,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_sup</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -387,7 +387,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>tot_daly_sup</t>
+          <t>tot_daly_up</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -402,7 +402,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>tot_medic_costs_sup</t>
+          <t>tot_medic_costs_up</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -417,7 +417,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>tot_soc_costs_sup</t>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
